--- a/artfynd/A 29174-2025 artfynd.xlsx
+++ b/artfynd/A 29174-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119715633</v>
+        <v>119715632</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455349</v>
+        <v>455359</v>
       </c>
       <c r="R2" t="n">
-        <v>6520808</v>
+        <v>6520827</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119715659</v>
+        <v>119715633</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455565</v>
+        <v>455349</v>
       </c>
       <c r="R3" t="n">
-        <v>6520793</v>
+        <v>6520808</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,37 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119715524</v>
+        <v>119715554</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>102992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Näktergal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Luscinia luscinia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +930,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455331</v>
+        <v>455291</v>
       </c>
       <c r="R4" t="n">
-        <v>6520835</v>
+        <v>6520782</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1020,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119715632</v>
+        <v>119715488</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455359</v>
+        <v>455507</v>
       </c>
       <c r="R5" t="n">
-        <v>6520827</v>
+        <v>6520809</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,12 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,32 +1115,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119715672</v>
+        <v>119715524</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>103037</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1175,7 +1150,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455512</v>
+        <v>455331</v>
       </c>
       <c r="R6" t="n">
-        <v>6520849</v>
+        <v>6520835</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,12 +1228,7 @@
         <v>119715650</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,37 +1335,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119715554</v>
+        <v>119715659</v>
       </c>
       <c r="B8" t="n">
-        <v>57943</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102992</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Näktergal</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Luscinia luscinia</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455291</v>
+        <v>455565</v>
       </c>
       <c r="R8" t="n">
-        <v>6520782</v>
+        <v>6520793</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1480,15 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119715488</v>
+        <v>119715669</v>
       </c>
       <c r="B9" t="n">
-        <v>57801</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1529,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455507</v>
+        <v>455604</v>
       </c>
       <c r="R9" t="n">
-        <v>6520809</v>
+        <v>6520889</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,12 +1519,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,58 +1555,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122234390</v>
+        <v>119715672</v>
       </c>
       <c r="B10" t="n">
-        <v>56282</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205992</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grimstorp, Vg</t>
+          <t>Ingelstorp, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455401</v>
+        <v>455512</v>
       </c>
       <c r="R10" t="n">
-        <v>6520787</v>
+        <v>6520849</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,17 +1629,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Inspelad med Wildlife acoustics Echo Meter Touch 2 PRO</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,27 +1649,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Eric Bjuringer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122234402</v>
+        <v>122234390</v>
       </c>
       <c r="B11" t="n">
-        <v>56294</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,21 +1676,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1817,6 +1770,113 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122234402</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Grimstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>455401</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6520787</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gullspång</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hova</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Inspelad med Wildlife acoustics Echo Meter Touch 2 PRO</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
